--- a/ap1.xlsx.xlsx
+++ b/ap1.xlsx.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\APOORVA\MIT CCE\2. SEM Contents\VIII sem\MTL 4-2-26 to 4-6-26\Project\Bussiness card\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6836703F-BC52-4489-892B-E066E72779A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{247C3C5F-7568-468D-A5BF-163623D9FE29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1140" yWindow="1140" windowWidth="14400" windowHeight="7270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>FirstName</t>
   </si>
@@ -106,6 +106,9 @@
   </si>
   <si>
     <t>MTL</t>
+  </si>
+  <si>
+    <t>Copies</t>
   </si>
 </sst>
 </file>
@@ -453,13 +456,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="15" width="10.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -505,8 +508,11 @@
       <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
+      <c r="P1" s="1" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="2" spans="1:15" ht="29" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>15</v>
       </c>
@@ -551,6 +557,9 @@
       </c>
       <c r="O2" s="2" t="s">
         <v>23</v>
+      </c>
+      <c r="P2" s="2">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
